--- a/data/trans_dic/P57_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Clase-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,27; 40,78</t>
+          <t>31,24; 40,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,62; 48,03</t>
+          <t>38,85; 48,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,16; 38,07</t>
+          <t>26,84; 37,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,51; 51,97</t>
+          <t>43,77; 51,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,01; 38,57</t>
+          <t>30,71; 37,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,6; 48,62</t>
+          <t>42,5; 48,67</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,24; 36,77</t>
+          <t>26,89; 37,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,96; 52,76</t>
+          <t>42,9; 52,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,33; 29,72</t>
+          <t>20,55; 29,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,83; 49,35</t>
+          <t>40,3; 48,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,32; 32,15</t>
+          <t>25,42; 32,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,62; 49,67</t>
+          <t>42,45; 49,43</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,1; 33,22</t>
+          <t>25,31; 33,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,13; 87,49</t>
+          <t>47,14; 86,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,41; 31,33</t>
+          <t>18,19; 32,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,14; 45,52</t>
+          <t>33,09; 45,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,65; 32,05</t>
+          <t>24,68; 31,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,85; 83,31</t>
+          <t>45,08; 82,14</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,46; 30,66</t>
+          <t>25,21; 30,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,78; 48,76</t>
+          <t>41,84; 49,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,17; 33,5</t>
+          <t>26,94; 33,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 44,12</t>
+          <t>19,06; 44,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,72; 30,95</t>
+          <t>26,9; 30,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,43; 45,01</t>
+          <t>27,64; 45,44</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,92; 28,03</t>
+          <t>20,76; 27,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,08; 48,98</t>
+          <t>38,88; 48,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,65; 21,32</t>
+          <t>15,9; 21,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,74; 34,25</t>
+          <t>22,91; 34,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,71; 23,48</t>
+          <t>18,98; 23,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,31; 38,26</t>
+          <t>29,06; 38,65</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,59; 50,64</t>
+          <t>38,8; 51,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52,6; 73,21</t>
+          <t>52,8; 73,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,12; 30,63</t>
+          <t>25,18; 30,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,42; 45,27</t>
+          <t>38,33; 45,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,88; 34,18</t>
+          <t>28,76; 33,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43,52; 50,83</t>
+          <t>43,49; 50,64</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,71; 31,95</t>
+          <t>28,72; 32,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46,41; 62,25</t>
+          <t>46,57; 63,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,84; 27,99</t>
+          <t>24,92; 27,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,0; 41,02</t>
+          <t>30,39; 41,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,21; 29,47</t>
+          <t>27,1; 29,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,63; 50,46</t>
+          <t>40,28; 50,51</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>133560; 174202</t>
+          <t>133459; 174273</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>195119; 242631</t>
+          <t>196268; 242682</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93734; 131380</t>
+          <t>92607; 128622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>194244; 231982</t>
+          <t>195413; 229644</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>239465; 297863</t>
+          <t>237153; 291541</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>405381; 462646</t>
+          <t>404433; 463136</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>102093; 137798</t>
+          <t>100770; 138815</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>194001; 238279</t>
+          <t>193743; 237455</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75034; 109648</t>
+          <t>75835; 108618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>155540; 188031</t>
+          <t>153548; 185983</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>188331; 239108</t>
+          <t>189084; 238530</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>354845; 413529</t>
+          <t>353464; 411510</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>130248; 172423</t>
+          <t>131366; 173678</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314929; 584634</t>
+          <t>315026; 579750</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30293; 51563</t>
+          <t>29930; 53741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55316; 75978</t>
+          <t>55232; 76356</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>168499; 219085</t>
+          <t>168700; 216257</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>374588; 695780</t>
+          <t>376534; 685981</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>291591; 351235</t>
+          <t>288818; 348804</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>429999; 501778</t>
+          <t>430582; 505022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>224141; 276312</t>
+          <t>222188; 277359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>178210; 429764</t>
+          <t>185711; 430545</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>526433; 609757</t>
+          <t>530084; 609753</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>529458; 901746</t>
+          <t>553632; 910388</t>
         </is>
       </c>
     </row>
@@ -1816,32 +1816,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>129381; 173374</t>
+          <t>128399; 170378</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>184706; 231462</t>
+          <t>183731; 230361</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115222; 156935</t>
+          <t>117031; 159929</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181994; 286717</t>
+          <t>191802; 288405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>253507; 318030</t>
+          <t>257088; 317389</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>370842; 501065</t>
+          <t>380577; 506285</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>110809; 145406</t>
+          <t>111424; 146461</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>126498; 176076</t>
+          <t>126990; 175767</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>270209; 329449</t>
+          <t>270810; 331291</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>289069; 340614</t>
+          <t>288407; 343741</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>393617; 465779</t>
+          <t>391921; 463019</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>432117; 504676</t>
+          <t>431859; 502864</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>968191; 1077407</t>
+          <t>968349; 1083050</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1562904; 2096252</t>
+          <t>1568126; 2135401</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>873031; 983770</t>
+          <t>876141; 982442</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1102895; 1459442</t>
+          <t>1081371; 1460668</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1873943; 2029429</t>
+          <t>1866206; 2024809</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2813837; 3494405</t>
+          <t>2789786; 3498025</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,24; 40,8</t>
+          <t>31,53; 40,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,85; 48,04</t>
+          <t>39,37; 48,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,84; 37,27</t>
+          <t>27,03; 37,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,77; 51,44</t>
+          <t>42,68; 50,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,71; 37,75</t>
+          <t>30,8; 37,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,5; 48,67</t>
+          <t>41,98; 48,04</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,89; 37,04</t>
+          <t>27,21; 37,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,9; 52,58</t>
+          <t>43,25; 53,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,55; 29,44</t>
+          <t>20,63; 30,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,3; 48,82</t>
+          <t>40,23; 48,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,42; 32,07</t>
+          <t>25,31; 32,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,45; 49,43</t>
+          <t>43,67; 49,91</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,31; 33,47</t>
+          <t>25,6; 33,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,14; 86,75</t>
+          <t>43,5; 52,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 32,65</t>
+          <t>17,56; 31,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,09; 45,75</t>
+          <t>33,57; 45,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,68; 31,64</t>
+          <t>24,68; 31,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,08; 82,14</t>
+          <t>41,56; 49,52</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,21; 30,45</t>
+          <t>25,3; 30,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,84; 49,07</t>
+          <t>41,73; 48,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,94; 33,63</t>
+          <t>27,02; 33,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,06; 44,2</t>
+          <t>40,13; 45,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,9; 30,95</t>
+          <t>26,98; 30,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,64; 45,44</t>
+          <t>41,98; 46,62</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,76; 27,54</t>
+          <t>20,88; 27,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,88; 48,75</t>
+          <t>37,12; 46,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,9; 21,73</t>
+          <t>15,55; 21,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,91; 34,45</t>
+          <t>30,7; 36,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,98; 23,43</t>
+          <t>18,81; 23,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,06; 38,65</t>
+          <t>34,19; 38,96</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,8; 51,01</t>
+          <t>39,18; 51,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52,8; 73,08</t>
+          <t>52,45; 72,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,18; 30,8</t>
+          <t>25,17; 30,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,33; 45,68</t>
+          <t>39,28; 46,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,76; 33,98</t>
+          <t>28,8; 33,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43,49; 50,64</t>
+          <t>43,44; 50,2</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,72; 32,12</t>
+          <t>28,87; 32,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46,57; 63,42</t>
+          <t>44,34; 48,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,92; 27,95</t>
+          <t>24,93; 27,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,39; 41,05</t>
+          <t>39,73; 42,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,1; 29,4</t>
+          <t>27,3; 29,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,28; 50,51</t>
+          <t>42,45; 44,85</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>220224</t>
+          <t>241597</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213263</t>
+          <t>227331</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>433487</t>
+          <t>468928</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>133459; 174273</t>
+          <t>134690; 173795</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>196268; 242682</t>
+          <t>216796; 266884</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92607; 128622</t>
+          <t>93260; 128678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>195413; 229644</t>
+          <t>207972; 246182</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>237153; 291541</t>
+          <t>237846; 291667</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>404433; 463136</t>
+          <t>435681; 498555</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>214912</t>
+          <t>232567</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>170810</t>
+          <t>189044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>385722</t>
+          <t>421611</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>100770; 138815</t>
+          <t>101965; 140147</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>193743; 237455</t>
+          <t>208713; 256946</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75835; 108618</t>
+          <t>76140; 111235</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>153548; 185983</t>
+          <t>169538; 205265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>189084; 238530</t>
+          <t>188227; 237975</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>353464; 411510</t>
+          <t>394755; 451176</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>450593</t>
+          <t>226347</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64755</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>515348</t>
+          <t>300163</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>131366; 173678</t>
+          <t>132834; 174082</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315026; 579750</t>
+          <t>205155; 247562</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29930; 53741</t>
+          <t>28897; 52447</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55232; 76356</t>
+          <t>62942; 85883</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>168700; 216257</t>
+          <t>168718; 218022</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>376534; 685981</t>
+          <t>273928; 326395</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>465969</t>
+          <t>506943</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>331843</t>
+          <t>368335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>797812</t>
+          <t>875279</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>288818; 348804</t>
+          <t>289822; 350030</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>430582; 505022</t>
+          <t>469642; 544119</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>222188; 277359</t>
+          <t>222855; 274685</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>185711; 430545</t>
+          <t>343745; 393524</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>530084; 609753</t>
+          <t>531505; 609592</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>553632; 910388</t>
+          <t>832067; 924095</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>206441</t>
+          <t>236328</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>250189</t>
+          <t>273680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>456630</t>
+          <t>510008</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>128399; 170378</t>
+          <t>129130; 172201</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>183731; 230361</t>
+          <t>209852; 261266</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117031; 159929</t>
+          <t>114464; 155329</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>191802; 288405</t>
+          <t>253727; 298834</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>257088; 317389</t>
+          <t>254792; 316180</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>380577; 506285</t>
+          <t>475848; 542264</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>153763</t>
+          <t>150265</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314735</t>
+          <t>353794</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>468499</t>
+          <t>504059</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>111424; 146461</t>
+          <t>112505; 146696</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>126990; 175767</t>
+          <t>124429; 170943</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>270810; 331291</t>
+          <t>270727; 330785</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>288407; 343741</t>
+          <t>328350; 384559</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>391921; 463019</t>
+          <t>392540; 461126</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>431859; 502864</t>
+          <t>466154; 538663</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1711902</t>
+          <t>1594045</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1345595</t>
+          <t>1486001</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3057497</t>
+          <t>3080047</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>968349; 1083050</t>
+          <t>973646; 1084521</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1568126; 2135401</t>
+          <t>1522212; 1656190</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>876141; 982442</t>
+          <t>876332; 982711</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1081371; 1460668</t>
+          <t>1436245; 1540784</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1866206; 2024809</t>
+          <t>1880431; 2028672</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2789786; 3498025</t>
+          <t>2992156; 3161226</t>
         </is>
       </c>
     </row>
